--- a/data/trans_bre/P1404-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1404-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 9,25</t>
+          <t>0,55; 9,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 8,23</t>
+          <t>-2,11; 8,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 7,04</t>
+          <t>-5,17; 6,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,93</t>
+          <t>-3,05; 6,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 255,69</t>
+          <t>1,98; 256,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 119,06</t>
+          <t>-19,74; 114,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 74,7</t>
+          <t>-33,1; 69,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 67,25</t>
+          <t>-20,39; 59,57</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 6,03</t>
+          <t>-1,32; 5,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 7,39</t>
+          <t>-2,32; 6,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 7,55</t>
+          <t>-1,34; 7,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,44</t>
+          <t>-2,53; 5,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 103,81</t>
+          <t>-13,48; 97,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 68,56</t>
+          <t>-15,12; 67,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 79,59</t>
+          <t>-10,12; 76,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 57,87</t>
+          <t>-17,62; 52,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 4,38</t>
+          <t>-4,32; 4,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 7,53</t>
+          <t>-2,46; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 7,22</t>
+          <t>-3,6; 7,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 6,26</t>
+          <t>-2,79; 6,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,99; 72,78</t>
+          <t>-42,17; 67,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 91,17</t>
+          <t>-18,91; 93,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 68,48</t>
+          <t>-22,93; 72,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 51,07</t>
+          <t>-16,68; 48,0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-17,79%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,75</t>
+          <t>-4,04; 2,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 9,09</t>
+          <t>-1,19; 9,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 7,6</t>
+          <t>-2,74; 6,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 2,76</t>
+          <t>-5,3; 5,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,91; 61,97</t>
+          <t>-48,46; 62,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 99,59</t>
+          <t>-8,0; 101,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 76,11</t>
+          <t>-18,57; 68,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,56; 18,86</t>
+          <t>-27,18; 43,2</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,28</t>
+          <t>-6,82; 5,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 13,63</t>
+          <t>-2,09; 13,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 8,3</t>
+          <t>-4,44; 7,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 11,91</t>
+          <t>-0,69; 10,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,42; 69,43</t>
+          <t>-47,23; 72,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 112,28</t>
+          <t>-10,85; 101,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 85,98</t>
+          <t>-27,34; 83,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 71,84</t>
+          <t>-2,46; 64,91</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,11</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-14,95%</t>
+          <t>-13,14%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 12,71</t>
+          <t>3,02; 12,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 7,77</t>
+          <t>-4,54; 7,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 5,41</t>
+          <t>-5,12; 5,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 2,19</t>
+          <t>-7,73; 2,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,3; 320,47</t>
+          <t>33,69; 337,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 72,07</t>
+          <t>-26,29; 69,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 69,14</t>
+          <t>-39,92; 79,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,26; 12,23</t>
+          <t>-33,47; 14,66</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,23</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>139,36%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,81</t>
+          <t>1,28; 7,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,08</t>
+          <t>-3,32; 3,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 3,42</t>
+          <t>-3,87; 3,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 57,31</t>
+          <t>-2,19; 5,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,56; 153,2</t>
+          <t>16,43; 158,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 43,08</t>
+          <t>-26,17; 42,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 37,12</t>
+          <t>-30,64; 34,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 372,19</t>
+          <t>-11,27; 36,94</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 4,39</t>
+          <t>-2,09; 4,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 6,0</t>
+          <t>-0,04; 5,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,18</t>
+          <t>0,6; 7,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 11,88</t>
+          <t>-0,14; 5,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 45,19</t>
+          <t>-17,56; 44,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 86,35</t>
+          <t>-1,96; 81,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,21; 81,86</t>
+          <t>3,66; 81,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,71; 267,5</t>
+          <t>-1,2; 57,42</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,75</t>
+          <t>1,03; 3,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,1</t>
+          <t>0,66; 3,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,34</t>
+          <t>0,18; 3,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 23,11</t>
+          <t>0,13; 3,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,48; 51,37</t>
+          <t>12,4; 54,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,66; 39,16</t>
+          <t>4,85; 37,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 31,67</t>
+          <t>1,51; 32,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,24; 180,81</t>
+          <t>0,83; 24,69</t>
         </is>
       </c>
     </row>
